--- a/output/graficos_regionales_cobertura/plot_regional_cobertura_2024_nuble.xlsx
+++ b/output/graficos_regionales_cobertura/plot_regional_cobertura_2024_nuble.xlsx
@@ -9,7 +9,8 @@
   <sheets>
     <sheet name="Total_Regional" sheetId="1" r:id="rId1"/>
     <sheet name="Por_Sexo" sheetId="2" r:id="rId2"/>
-    <sheet name="Por_Edad" sheetId="3" r:id="rId3"/>
+    <sheet name="Por_Prov" sheetId="3" r:id="rId3"/>
+    <sheet name="Por_Edad" sheetId="4" r:id="rId4"/>
   </sheets>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -353,7 +354,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B2"/>
+  <dimension ref="A1:E2"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -364,19 +365,44 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
+          <t>Residentes</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Proyectada</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
           <t>Cobertura</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Categoria_lbl</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Total
-Regional</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="B2">
+        <v>533497</v>
+      </c>
+      <c r="C2">
+        <v>521711</v>
+      </c>
+      <c r="D2">
         <v>102.259105136752</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
       </c>
     </row>
   </sheetData>
@@ -465,7 +491,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E6"/>
+  <dimension ref="A1:E4"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -476,7 +502,7 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>Tramo_Edad</t>
+          <t>Provincia</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
@@ -503,17 +529,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>0-14</t>
+          <t>Itata</t>
         </is>
       </c>
       <c r="C2">
-        <v>66966</v>
+        <v>56660</v>
       </c>
       <c r="D2">
-        <v>65261</v>
+        <v>56654</v>
       </c>
       <c r="E2">
-        <v>102.6125863839046</v>
+        <v>100.0105906026053</v>
       </c>
     </row>
     <row r="3">
@@ -524,17 +550,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>15-29</t>
+          <t>Punilla</t>
         </is>
       </c>
       <c r="C3">
-        <v>104136</v>
+        <v>118034</v>
       </c>
       <c r="D3">
-        <v>95179</v>
+        <v>114934</v>
       </c>
       <c r="E3">
-        <v>109.410689332731</v>
+        <v>102.6972001322498</v>
       </c>
     </row>
     <row r="4">
@@ -545,17 +571,117 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>30-44</t>
+          <t>Diguillín</t>
         </is>
       </c>
       <c r="C4">
-        <v>113213</v>
+        <v>358803</v>
       </c>
       <c r="D4">
-        <v>104623</v>
+        <v>350123</v>
       </c>
       <c r="E4">
-        <v>108.2104317406307</v>
+        <v>102.4791287633203</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:E18"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" s="1" customFormat="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Desagregación 1</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Tramo_Edad</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Residentes</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Proyectada</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Cobertura</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>0-4</t>
+        </is>
+      </c>
+      <c r="C2">
+        <v>18246</v>
+      </c>
+      <c r="D2">
+        <v>17194</v>
+      </c>
+      <c r="E2">
+        <v>106.1184134000233</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>5-9</t>
+        </is>
+      </c>
+      <c r="C3">
+        <v>14968</v>
+      </c>
+      <c r="D3">
+        <v>14254</v>
+      </c>
+      <c r="E3">
+        <v>105.0091202469482</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>10-14</t>
+        </is>
+      </c>
+      <c r="C4">
+        <v>33752</v>
+      </c>
+      <c r="D4">
+        <v>33813</v>
+      </c>
+      <c r="E4">
+        <v>99.81959601336764</v>
       </c>
     </row>
     <row r="5">
@@ -566,17 +692,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>45-64</t>
+          <t>15-19</t>
         </is>
       </c>
       <c r="C5">
-        <v>141463</v>
+        <v>34647</v>
       </c>
       <c r="D5">
-        <v>139785</v>
+        <v>32956</v>
       </c>
       <c r="E5">
-        <v>101.2004149229173</v>
+        <v>105.1310838694016</v>
       </c>
     </row>
     <row r="6">
@@ -587,17 +713,269 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>65+</t>
+          <t>20-24</t>
         </is>
       </c>
       <c r="C6">
-        <v>89713</v>
+        <v>33627</v>
       </c>
       <c r="D6">
-        <v>90407</v>
+        <v>29823</v>
       </c>
       <c r="E6">
-        <v>99.23236032608095</v>
+        <v>112.7552560104617</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>25-29</t>
+        </is>
+      </c>
+      <c r="C7">
+        <v>35862</v>
+      </c>
+      <c r="D7">
+        <v>32400</v>
+      </c>
+      <c r="E7">
+        <v>110.6851851851852</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>30-34</t>
+        </is>
+      </c>
+      <c r="C8">
+        <v>39883</v>
+      </c>
+      <c r="D8">
+        <v>36395</v>
+      </c>
+      <c r="E8">
+        <v>109.5837340293997</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>35-39</t>
+        </is>
+      </c>
+      <c r="C9">
+        <v>38095</v>
+      </c>
+      <c r="D9">
+        <v>34915</v>
+      </c>
+      <c r="E9">
+        <v>109.1078333094658</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>40-44</t>
+        </is>
+      </c>
+      <c r="C10">
+        <v>35235</v>
+      </c>
+      <c r="D10">
+        <v>33313</v>
+      </c>
+      <c r="E10">
+        <v>105.7695194068382</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>45-49</t>
+        </is>
+      </c>
+      <c r="C11">
+        <v>32410</v>
+      </c>
+      <c r="D11">
+        <v>33456</v>
+      </c>
+      <c r="E11">
+        <v>96.87350549976088</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>50-54</t>
+        </is>
+      </c>
+      <c r="C12">
+        <v>37451</v>
+      </c>
+      <c r="D12">
+        <v>36737</v>
+      </c>
+      <c r="E12">
+        <v>101.9435446552522</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>55-59</t>
+        </is>
+      </c>
+      <c r="C13">
+        <v>36939</v>
+      </c>
+      <c r="D13">
+        <v>36403</v>
+      </c>
+      <c r="E13">
+        <v>101.4724061203747</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>60-64</t>
+        </is>
+      </c>
+      <c r="C14">
+        <v>34663</v>
+      </c>
+      <c r="D14">
+        <v>33189</v>
+      </c>
+      <c r="E14">
+        <v>104.4412305281871</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>65-69</t>
+        </is>
+      </c>
+      <c r="C15">
+        <v>28874</v>
+      </c>
+      <c r="D15">
+        <v>28670</v>
+      </c>
+      <c r="E15">
+        <v>100.7115451691664</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>70-74</t>
+        </is>
+      </c>
+      <c r="C16">
+        <v>22249</v>
+      </c>
+      <c r="D16">
+        <v>22742</v>
+      </c>
+      <c r="E16">
+        <v>97.83220473133409</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>75-79</t>
+        </is>
+      </c>
+      <c r="C17">
+        <v>16582</v>
+      </c>
+      <c r="D17">
+        <v>16698</v>
+      </c>
+      <c r="E17">
+        <v>99.30530602467361</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>80+</t>
+        </is>
+      </c>
+      <c r="C18">
+        <v>22008</v>
+      </c>
+      <c r="D18">
+        <v>22297</v>
+      </c>
+      <c r="E18">
+        <v>98.7038615060322</v>
       </c>
     </row>
   </sheetData>

--- a/output/graficos_regionales_cobertura/plot_regional_cobertura_2024_nuble.xlsx
+++ b/output/graficos_regionales_cobertura/plot_regional_cobertura_2024_nuble.xlsx
@@ -418,7 +418,7 @@
     <row r="1" s="1" customFormat="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Desagregación 1</t>
+          <t>region</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
@@ -497,7 +497,7 @@
     <row r="1" s="1" customFormat="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Desagregación 1</t>
+          <t>region</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
@@ -597,7 +597,7 @@
     <row r="1" s="1" customFormat="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Desagregación 1</t>
+          <t>region</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">

--- a/output/graficos_regionales_cobertura/plot_regional_cobertura_2024_nuble.xlsx
+++ b/output/graficos_regionales_cobertura/plot_regional_cobertura_2024_nuble.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="44">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="47" uniqueCount="47">
   <si>
     <t xml:space="preserve">Categoria</t>
   </si>
@@ -48,7 +48,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-07-27 21:15</t>
+    <t xml:space="preserve">2026-08-07 07:13</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -60,16 +60,25 @@
     <t xml:space="preserve">Imagen asociada</t>
   </si>
   <si>
-    <t xml:space="preserve"/>
+    <t xml:space="preserve">plot_regional_cobertura_2024_nuble.png</t>
   </si>
   <si>
     <t xml:space="preserve">Indicador</t>
   </si>
   <si>
+    <t xml:space="preserve">Cobertura de residentes</t>
+  </si>
+  <si>
     <t xml:space="preserve">Unidad territorial</t>
   </si>
   <si>
+    <t xml:space="preserve">Region de Ñuble</t>
+  </si>
+  <si>
     <t xml:space="preserve">Año</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2024</t>
   </si>
   <si>
     <t xml:space="preserve">region</t>
@@ -609,23 +618,23 @@
         <v>14</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>13</v>
+        <v>19</v>
       </c>
     </row>
   </sheetData>
@@ -648,10 +657,10 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>1</v>
@@ -665,10 +674,10 @@
     </row>
     <row r="2">
       <c r="A2" s="2" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="C2" s="2" t="n">
         <v>262121</v>
@@ -682,10 +691,10 @@
     </row>
     <row r="3">
       <c r="A3" s="2" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="C3" s="2" t="n">
         <v>271376</v>
@@ -718,10 +727,10 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>1</v>
@@ -735,10 +744,10 @@
     </row>
     <row r="2">
       <c r="A2" s="2" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="C2" s="2" t="n">
         <v>56660</v>
@@ -752,10 +761,10 @@
     </row>
     <row r="3">
       <c r="A3" s="2" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="C3" s="2" t="n">
         <v>118034</v>
@@ -769,10 +778,10 @@
     </row>
     <row r="4">
       <c r="A4" s="2" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="C4" s="2" t="n">
         <v>358803</v>
@@ -805,10 +814,10 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>1</v>
@@ -822,10 +831,10 @@
     </row>
     <row r="2">
       <c r="A2" s="2" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="C2" s="2" t="n">
         <v>18246</v>
@@ -839,10 +848,10 @@
     </row>
     <row r="3">
       <c r="A3" s="2" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="C3" s="2" t="n">
         <v>14968</v>
@@ -856,10 +865,10 @@
     </row>
     <row r="4">
       <c r="A4" s="2" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="C4" s="2" t="n">
         <v>33752</v>
@@ -873,10 +882,10 @@
     </row>
     <row r="5">
       <c r="A5" s="2" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="C5" s="2" t="n">
         <v>34647</v>
@@ -890,10 +899,10 @@
     </row>
     <row r="6">
       <c r="A6" s="2" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="C6" s="2" t="n">
         <v>33627</v>
@@ -907,10 +916,10 @@
     </row>
     <row r="7">
       <c r="A7" s="2" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="C7" s="2" t="n">
         <v>35862</v>
@@ -924,10 +933,10 @@
     </row>
     <row r="8">
       <c r="A8" s="2" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="C8" s="2" t="n">
         <v>39883</v>
@@ -941,10 +950,10 @@
     </row>
     <row r="9">
       <c r="A9" s="2" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="C9" s="2" t="n">
         <v>38095</v>
@@ -958,10 +967,10 @@
     </row>
     <row r="10">
       <c r="A10" s="2" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="C10" s="2" t="n">
         <v>35235</v>
@@ -975,10 +984,10 @@
     </row>
     <row r="11">
       <c r="A11" s="2" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="C11" s="2" t="n">
         <v>32410</v>
@@ -992,10 +1001,10 @@
     </row>
     <row r="12">
       <c r="A12" s="2" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="C12" s="2" t="n">
         <v>37451</v>
@@ -1009,10 +1018,10 @@
     </row>
     <row r="13">
       <c r="A13" s="2" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="C13" s="2" t="n">
         <v>36939</v>
@@ -1026,10 +1035,10 @@
     </row>
     <row r="14">
       <c r="A14" s="2" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="C14" s="2" t="n">
         <v>34663</v>
@@ -1043,10 +1052,10 @@
     </row>
     <row r="15">
       <c r="A15" s="2" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="C15" s="2" t="n">
         <v>28874</v>
@@ -1060,10 +1069,10 @@
     </row>
     <row r="16">
       <c r="A16" s="2" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="C16" s="2" t="n">
         <v>22249</v>
@@ -1077,10 +1086,10 @@
     </row>
     <row r="17">
       <c r="A17" s="2" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="C17" s="2" t="n">
         <v>16582</v>
@@ -1094,10 +1103,10 @@
     </row>
     <row r="18">
       <c r="A18" s="2" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="C18" s="2" t="n">
         <v>22008</v>

--- a/output/graficos_regionales_cobertura/plot_regional_cobertura_2024_nuble.xlsx
+++ b/output/graficos_regionales_cobertura/plot_regional_cobertura_2024_nuble.xlsx
@@ -48,7 +48,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-08-07 07:13</t>
+    <t xml:space="preserve">2026-08-28 11:14</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -837,13 +837,13 @@
         <v>30</v>
       </c>
       <c r="C2" s="2" t="n">
-        <v>18246</v>
+        <v>20816</v>
       </c>
       <c r="D2" s="2" t="n">
-        <v>17194</v>
+        <v>26961</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>106.12</v>
+        <v>77.21</v>
       </c>
     </row>
     <row r="3">
@@ -854,13 +854,13 @@
         <v>31</v>
       </c>
       <c r="C3" s="2" t="n">
-        <v>14968</v>
+        <v>30404</v>
       </c>
       <c r="D3" s="2" t="n">
-        <v>14254</v>
+        <v>30943</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>105.01</v>
+        <v>98.26</v>
       </c>
     </row>
     <row r="4">

--- a/output/graficos_regionales_cobertura/plot_regional_cobertura_2024_nuble.xlsx
+++ b/output/graficos_regionales_cobertura/plot_regional_cobertura_2024_nuble.xlsx
@@ -48,7 +48,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-08-28 11:14</t>
+    <t xml:space="preserve">2026-09-01 13:24</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_regionales_cobertura/plot_regional_cobertura_2024_nuble.xlsx
+++ b/output/graficos_regionales_cobertura/plot_regional_cobertura_2024_nuble.xlsx
@@ -48,7 +48,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-01 13:24</t>
+    <t xml:space="preserve">2026-09-06 17:20</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_regionales_cobertura/plot_regional_cobertura_2024_nuble.xlsx
+++ b/output/graficos_regionales_cobertura/plot_regional_cobertura_2024_nuble.xlsx
@@ -48,7 +48,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-06 17:20</t>
+    <t xml:space="preserve">2026-09-08 13:53</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
